--- a/Project2.5/0910 -EOS#2 – To-do list for projects 2.5.xlsx
+++ b/Project2.5/0910 -EOS#2 – To-do list for projects 2.5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\Dropbox\Commisioner Roest\DatabaseClass-CSCI331\Projects\Project 3 Building Integrated Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9114920-E1B0-4BEB-92B1-C2C07E410A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6DFB5CE-E3E3-4272-BE9B-7FF1110AB594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Prabhjot Kaur" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="73">
   <si>
     <t>To-do list</t>
   </si>
@@ -92,49 +92,79 @@
     <t>Number Of Days</t>
   </si>
   <si>
+    <t xml:space="preserve"> Notes</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t>Column3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planning - Figuring Roles </t>
+  </si>
+  <si>
+    <t>1 day</t>
+  </si>
+  <si>
+    <t>assigned work to each members</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparation - Communicating with others </t>
+  </si>
+  <si>
+    <t>Discussed with Frankie about work distribution within group members</t>
+  </si>
+  <si>
+    <t>Add/remove columns for normalization</t>
+  </si>
+  <si>
+    <t>2 days</t>
+  </si>
+  <si>
+    <t>dropped and added some columns to make it look (cleaner) normalized.</t>
+  </si>
+  <si>
+    <t>Create Process.WorkflowSteps table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Created schema and table in the database </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assist others if groupmates are unavailable </t>
+  </si>
+  <si>
+    <t>3 days</t>
+  </si>
+  <si>
+    <t>Gave reminders about deadlines and assisted with instructions and tasks.</t>
+  </si>
+  <si>
+    <t>Create a .bak backup file of the final database</t>
+  </si>
+  <si>
+    <t>Paperwork - GITHUB</t>
+  </si>
+  <si>
+    <t>pushed file in github</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hand-off </t>
+  </si>
+  <si>
+    <t>Follow-up with Frankie</t>
+  </si>
+  <si>
+    <t>Name Salvador Cardoso</t>
+  </si>
+  <si>
+    <t>Project 1</t>
+  </si>
+  <si>
     <t>Revision Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planning - Figuring Roles </t>
-  </si>
-  <si>
-    <t>1 day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preparation - Communicating with others </t>
-  </si>
-  <si>
-    <t>Add/remove columns for normalization</t>
-  </si>
-  <si>
-    <t>2 days</t>
-  </si>
-  <si>
-    <t>Create Process.WorkflowSteps table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assist others if groupmates are unavailable </t>
-  </si>
-  <si>
-    <t>3 days</t>
-  </si>
-  <si>
-    <t>Create a .bak backup file of the final database</t>
-  </si>
-  <si>
-    <t>Paperwork - GITHUB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hand-off </t>
-  </si>
-  <si>
-    <t>Follow-up with Frankie</t>
-  </si>
-  <si>
-    <t>Name Salvador Cardoso</t>
-  </si>
-  <si>
-    <t>Project 1</t>
   </si>
   <si>
     <t xml:space="preserve">Planning - Understanding project </t>
@@ -404,7 +434,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -421,6 +451,14 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="4">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -429,12 +467,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -459,7 +491,7 @@
     <cellStyle name="Percent" xfId="5" builtinId="5"/>
     <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="19">
     <dxf>
       <font>
         <b val="0"/>
@@ -629,6 +661,18 @@
       </fill>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -748,13 +792,13 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="To-do list for projects">
     <tableStyle name="To-do list for projects" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="14"/>
-      <tableStyleElement type="headerRow" dxfId="13"/>
-      <tableStyleElement type="totalRow" dxfId="12"/>
-      <tableStyleElement type="firstColumn" dxfId="11"/>
-      <tableStyleElement type="lastColumn" dxfId="10"/>
-      <tableStyleElement type="firstRowStripe" dxfId="9"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="8"/>
+      <tableStyleElement type="wholeTable" dxfId="18"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstColumn" dxfId="15"/>
+      <tableStyleElement type="lastColumn" dxfId="14"/>
+      <tableStyleElement type="firstRowStripe" dxfId="13"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="12"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -769,16 +813,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{4076D023-3123-4435-9B03-717B351FB214}" name="Project167" displayName="Project167" ref="B7:H16" totalsRowShown="0">
-  <autoFilter ref="B7:H16" xr:uid="{A46E5AE3-66B6-48F2-9036-DC0EC84EE724}"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{4076D023-3123-4435-9B03-717B351FB214}" name="Project167" displayName="Project167" ref="B7:K16" totalsRowShown="0">
+  <autoFilter ref="B7:K16" xr:uid="{A46E5AE3-66B6-48F2-9036-DC0EC84EE724}"/>
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{52333874-C2BC-4FBF-9AA5-5291ED527120}" name="% done" dataCellStyle="Percent"/>
     <tableColumn id="2" xr3:uid="{B01D3C54-85C7-4AC4-B550-F441F081A8E7}" name="Phase" dataCellStyle="Normal"/>
     <tableColumn id="5" xr3:uid="{4A96FAF1-6CFF-4C95-A1B9-D6A409D17E24}" name="Start By"/>
     <tableColumn id="7" xr3:uid="{288AAF48-94FD-483E-BC80-43361A2172AA}" name="Original Due By"/>
     <tableColumn id="3" xr3:uid="{079E2D1B-453B-4EE7-A63C-A52ADC49D9FF}" name="Revised Due By" dataCellStyle="Date"/>
-    <tableColumn id="8" xr3:uid="{391FA284-95B3-4A59-A408-B42F0990F555}" name="Number Of Days" dataDxfId="7" dataCellStyle="Date"/>
-    <tableColumn id="4" xr3:uid="{3331DA69-AA66-4458-9EB4-B030D208F716}" name="Revision Notes"/>
+    <tableColumn id="8" xr3:uid="{391FA284-95B3-4A59-A408-B42F0990F555}" name="Number Of Days" dataDxfId="11" dataCellStyle="Date"/>
+    <tableColumn id="4" xr3:uid="{3331DA69-AA66-4458-9EB4-B030D208F716}" name=" Notes" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{806F6EC5-FD69-4C62-949A-EB86203BF4FE}" name="Column1" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{682DAA65-0962-4196-AD97-90717D5349A7}" name="Column2" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{AF62FB75-0DC9-4CC3-9FB7-F33E3D933047}" name="Column3" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="To-do list for projects" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -1284,7 +1331,7 @@
     <tabColor theme="5" tint="0.79998168889431442"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:H16"/>
+  <dimension ref="B1:L16"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.140625" customWidth="1"/>
@@ -1298,7 +1345,7 @@
     <col min="10" max="10" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" s="1" customFormat="1" ht="42.75" customHeight="1">
+    <row r="1" spans="2:12" s="1" customFormat="1" ht="42.75" customHeight="1">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1309,46 +1356,46 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1"/>
-    <row r="3" spans="2:8" s="1" customFormat="1" ht="18" customHeight="1">
-      <c r="B3" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11"/>
+    <row r="2" spans="2:12" ht="15" customHeight="1"/>
+    <row r="3" spans="2:12" s="1" customFormat="1" ht="18" customHeight="1">
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="13"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="14"/>
-    </row>
-    <row r="4" spans="2:8" s="1" customFormat="1" ht="18" customHeight="1">
-      <c r="B4" s="11" t="s">
+      <c r="G3" s="15"/>
+      <c r="H3" s="16"/>
+    </row>
+    <row r="4" spans="2:12" s="1" customFormat="1" ht="18" customHeight="1">
+      <c r="B4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="11"/>
+      <c r="C4" s="13"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="7"/>
-      <c r="H4" s="8"/>
-    </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1"/>
-    <row r="6" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="B6" s="15" t="s">
+      <c r="G4" s="11"/>
+      <c r="H4" s="12"/>
+    </row>
+    <row r="5" spans="2:12" ht="15" customHeight="1"/>
+    <row r="6" spans="2:12" s="1" customFormat="1" ht="30" customHeight="1">
+      <c r="B6" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-    </row>
-    <row r="7" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+    </row>
+    <row r="7" spans="2:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B7" t="s">
         <v>6</v>
       </c>
@@ -1367,180 +1414,229 @@
       <c r="G7" t="s">
         <v>11</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
+      <c r="I7" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B8" s="3">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="9">
+        <v>16</v>
+      </c>
+      <c r="D8" s="6">
         <v>46156</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="6">
         <v>46156</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8"/>
-    </row>
-    <row r="9" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
+        <v>17</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+    </row>
+    <row r="9" spans="2:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B9" s="3">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="9">
+        <v>19</v>
+      </c>
+      <c r="D9" s="6">
         <v>46156</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="6">
         <v>46156</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9"/>
-    </row>
-    <row r="10" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
+        <v>17</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="9"/>
+    </row>
+    <row r="10" spans="2:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B10" s="3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="9">
+        <v>21</v>
+      </c>
+      <c r="D10" s="6">
         <v>46157</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="6">
         <v>46158</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10"/>
-    </row>
-    <row r="11" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
+        <v>22</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+    </row>
+    <row r="11" spans="2:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B11" s="3">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="9">
+        <v>24</v>
+      </c>
+      <c r="D11" s="6">
         <v>46157</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="6">
         <v>46158</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11"/>
-    </row>
-    <row r="12" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
+        <v>22</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+    </row>
+    <row r="12" spans="2:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="9">
+        <v>26</v>
+      </c>
+      <c r="D12" s="6">
         <v>46157</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="6">
         <v>46159</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12"/>
-    </row>
-    <row r="13" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
+        <v>27</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+    </row>
+    <row r="13" spans="2:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="9">
+        <v>29</v>
+      </c>
+      <c r="D13" s="6">
         <v>46159</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="6">
         <v>46159</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13"/>
-    </row>
-    <row r="14" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
+        <v>17</v>
+      </c>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+    </row>
+    <row r="14" spans="2:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="10">
+        <v>30</v>
+      </c>
+      <c r="D14" s="7">
         <v>46157</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="6">
         <v>46159</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14"/>
-    </row>
-    <row r="15" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
+        <v>22</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+    </row>
+    <row r="15" spans="2:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="10">
-        <v>46158</v>
-      </c>
-      <c r="E15" s="9">
+        <v>32</v>
+      </c>
+      <c r="D15" s="7">
+        <v>46158</v>
+      </c>
+      <c r="E15" s="6">
         <v>46159</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15"/>
-    </row>
-    <row r="16" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
+        <v>22</v>
+      </c>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+    </row>
+    <row r="16" spans="2:12" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="9">
-        <v>46158</v>
-      </c>
-      <c r="E16" s="9">
+        <v>33</v>
+      </c>
+      <c r="D16" s="6">
+        <v>46158</v>
+      </c>
+      <c r="E16" s="6">
         <v>46159</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H16"/>
+        <v>22</v>
+      </c>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1569,7 +1665,7 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Percent done in this column under this heading. Data bar showing Percent done is automatically updated in each row. Use heading filters to find specific entries" sqref="B7" xr:uid="{369A205A-BF3F-469C-8133-9EAF0DDB42D8}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter project Phase in this column under this heading" sqref="C7" xr:uid="{0E0FDB92-D7C1-4327-878A-F2DD407ECC8B}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Due By date in this column under this heading" sqref="D7:G7" xr:uid="{A5934E8D-92A1-4465-9708-A2C4C562F896}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Notes in this column under this heading" sqref="H7" xr:uid="{1CB1329A-3E47-499C-A9E9-F63E54DF4878}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Notes in this column under this heading" sqref="H7:K7" xr:uid="{1CB1329A-3E47-499C-A9E9-F63E54DF4878}"/>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.25" footer="0.25"/>
@@ -1613,42 +1709,42 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1"/>
     <row r="3" spans="2:8" s="1" customFormat="1" ht="18" customHeight="1">
-      <c r="B3" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11"/>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="13"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
-      <c r="F3" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="14"/>
+      <c r="F3" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="15"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="2:8" s="1" customFormat="1" ht="18" customHeight="1">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="11"/>
+      <c r="C4" s="13"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="7"/>
-      <c r="H4" s="8"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="12"/>
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1"/>
     <row r="6" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="B6" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
+      <c r="B6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
     </row>
     <row r="7" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B7" t="s">
@@ -1670,7 +1766,7 @@
         <v>11</v>
       </c>
       <c r="H7" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
@@ -1678,17 +1774,17 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="9">
+        <v>37</v>
+      </c>
+      <c r="D8" s="6">
         <v>46155</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="6">
         <v>46156</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H8"/>
     </row>
@@ -1697,150 +1793,150 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="9">
+        <v>38</v>
+      </c>
+      <c r="D9" s="6">
         <v>46155</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="6">
         <v>46156</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H9"/>
     </row>
     <row r="10" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B10" s="3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="9">
+        <v>39</v>
+      </c>
+      <c r="D10" s="6">
         <v>46156</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="6">
         <v>46157</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H10"/>
     </row>
     <row r="11" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B11" s="3">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="9">
+        <v>40</v>
+      </c>
+      <c r="D11" s="6">
         <v>46156</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="6">
         <v>46158</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H11"/>
     </row>
     <row r="12" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="9">
+        <v>26</v>
+      </c>
+      <c r="D12" s="6">
         <v>46157</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="6">
         <v>46159</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H12"/>
     </row>
     <row r="13" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="9">
+        <v>41</v>
+      </c>
+      <c r="D13" s="6">
         <v>46157</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="6">
         <v>46158</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H13"/>
     </row>
     <row r="14" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="10">
+        <v>30</v>
+      </c>
+      <c r="D14" s="7">
         <v>46157</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="6">
         <v>46159</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H14"/>
     </row>
     <row r="15" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="10">
-        <v>46158</v>
-      </c>
-      <c r="E15" s="9">
+        <v>42</v>
+      </c>
+      <c r="D15" s="7">
+        <v>46158</v>
+      </c>
+      <c r="E15" s="6">
         <v>46159</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H15"/>
     </row>
     <row r="16" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="9">
-        <v>46158</v>
-      </c>
-      <c r="E16" s="9">
+        <v>43</v>
+      </c>
+      <c r="D16" s="6">
+        <v>46158</v>
+      </c>
+      <c r="E16" s="6">
         <v>46159</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H16"/>
     </row>
@@ -1917,42 +2013,42 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1"/>
     <row r="3" spans="2:8" s="1" customFormat="1" ht="18" customHeight="1">
-      <c r="B3" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11"/>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="13"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
-      <c r="F3" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="14"/>
+      <c r="F3" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="15"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="2:8" s="1" customFormat="1" ht="18" customHeight="1">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="11"/>
+      <c r="C4" s="13"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="7"/>
-      <c r="H4" s="8"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="12"/>
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1"/>
     <row r="6" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="B6" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
+      <c r="B6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
     </row>
     <row r="7" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B7" t="s">
@@ -1974,7 +2070,7 @@
         <v>11</v>
       </c>
       <c r="H7" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
@@ -1982,17 +2078,17 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="9">
+        <v>45</v>
+      </c>
+      <c r="D8" s="6">
         <v>46156</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="6">
         <v>46156</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H8"/>
     </row>
@@ -2001,17 +2097,17 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="9">
+        <v>46</v>
+      </c>
+      <c r="D9" s="6">
         <v>46156</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="6">
         <v>46156</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H9"/>
     </row>
@@ -2020,135 +2116,135 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="9">
+        <v>47</v>
+      </c>
+      <c r="D10" s="6">
         <v>46156</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="6">
         <v>46156</v>
       </c>
       <c r="F10" s="4">
         <v>46157</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="H10" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B11" s="3">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="9">
+        <v>21</v>
+      </c>
+      <c r="D11" s="6">
         <v>46157</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="6">
         <v>46158</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H11"/>
     </row>
     <row r="12" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="9">
+        <v>24</v>
+      </c>
+      <c r="D12" s="6">
         <v>46157</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="6">
         <v>46158</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H12"/>
     </row>
     <row r="13" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" s="9">
-        <v>46158</v>
-      </c>
-      <c r="E13" s="9">
+        <v>50</v>
+      </c>
+      <c r="D13" s="6">
+        <v>46158</v>
+      </c>
+      <c r="E13" s="6">
         <v>46159</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H13"/>
     </row>
     <row r="14" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="10">
+        <v>30</v>
+      </c>
+      <c r="D14" s="7">
         <v>46157</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="6">
         <v>46159</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H14"/>
     </row>
     <row r="15" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="10">
-        <v>46158</v>
-      </c>
-      <c r="E15" s="9">
+        <v>42</v>
+      </c>
+      <c r="D15" s="7">
+        <v>46158</v>
+      </c>
+      <c r="E15" s="6">
         <v>46159</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H15"/>
     </row>
     <row r="16" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="9">
-        <v>46158</v>
-      </c>
-      <c r="E16" s="9">
+        <v>51</v>
+      </c>
+      <c r="D16" s="6">
+        <v>46158</v>
+      </c>
+      <c r="E16" s="6">
         <v>46159</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H16"/>
     </row>
@@ -2219,42 +2315,42 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1"/>
     <row r="3" spans="2:8" s="1" customFormat="1" ht="18" customHeight="1">
-      <c r="B3" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11"/>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="13"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
-      <c r="F3" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="14"/>
+      <c r="F3" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3" s="15"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="2:8" s="1" customFormat="1" ht="18" customHeight="1">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="11"/>
+      <c r="C4" s="13"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="7"/>
-      <c r="H4" s="8"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="12"/>
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1"/>
     <row r="6" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="B6" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
+      <c r="B6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
     </row>
     <row r="7" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B7" t="s">
@@ -2267,7 +2363,7 @@
         <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F7" t="s">
         <v>10</v>
@@ -2276,7 +2372,7 @@
         <v>11</v>
       </c>
       <c r="H7" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
@@ -2284,17 +2380,17 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="9">
+        <v>54</v>
+      </c>
+      <c r="D8" s="6">
         <v>46156</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="6">
         <v>46156</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H8"/>
     </row>
@@ -2303,17 +2399,17 @@
         <v>0.75</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="9">
+        <v>55</v>
+      </c>
+      <c r="D9" s="6">
         <v>46156</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="6">
         <v>46156</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H9"/>
     </row>
@@ -2322,17 +2418,17 @@
         <v>0.5</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="9">
+        <v>56</v>
+      </c>
+      <c r="D10" s="6">
         <v>46157</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="6">
         <v>46157</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H10"/>
     </row>
@@ -2341,17 +2437,17 @@
         <v>0.25</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="9">
+        <v>40</v>
+      </c>
+      <c r="D11" s="6">
         <v>46157</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="6">
         <v>46157</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H11"/>
     </row>
@@ -2360,17 +2456,17 @@
         <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="10">
-        <v>46158</v>
-      </c>
-      <c r="E12" s="9">
+        <v>57</v>
+      </c>
+      <c r="D12" s="7">
+        <v>46158</v>
+      </c>
+      <c r="E12" s="6">
         <v>46159</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H12"/>
     </row>
@@ -2379,17 +2475,17 @@
         <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" s="10">
-        <v>46158</v>
-      </c>
-      <c r="E13" s="9">
+        <v>58</v>
+      </c>
+      <c r="D13" s="7">
+        <v>46158</v>
+      </c>
+      <c r="E13" s="6">
         <v>46159</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H13"/>
     </row>
@@ -2398,17 +2494,17 @@
         <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="10">
+        <v>30</v>
+      </c>
+      <c r="D14" s="7">
         <v>46157</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="6">
         <v>46159</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H14"/>
     </row>
@@ -2417,17 +2513,17 @@
         <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="10">
-        <v>46158</v>
-      </c>
-      <c r="E15" s="9">
+        <v>42</v>
+      </c>
+      <c r="D15" s="7">
+        <v>46158</v>
+      </c>
+      <c r="E15" s="6">
         <v>46159</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H15"/>
     </row>
@@ -2436,17 +2532,17 @@
         <v>0</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="9">
-        <v>46158</v>
-      </c>
-      <c r="E16" s="9">
+        <v>43</v>
+      </c>
+      <c r="D16" s="6">
+        <v>46158</v>
+      </c>
+      <c r="E16" s="6">
         <v>46159</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H16"/>
     </row>
@@ -2515,42 +2611,42 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1"/>
     <row r="3" spans="2:8" s="1" customFormat="1" ht="18" customHeight="1">
-      <c r="B3" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11"/>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="13"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
-      <c r="F3" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="14"/>
+      <c r="F3" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" s="15"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="2:8" s="1" customFormat="1" ht="18" customHeight="1">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="11"/>
+      <c r="C4" s="13"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="7"/>
-      <c r="H4" s="8"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="12"/>
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1"/>
     <row r="6" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="B6" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
+      <c r="B6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
     </row>
     <row r="7" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B7" t="s">
@@ -2572,7 +2668,7 @@
         <v>11</v>
       </c>
       <c r="H7" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
@@ -2580,17 +2676,17 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="9">
+        <v>54</v>
+      </c>
+      <c r="D8" s="6">
         <v>46156</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="6">
         <v>46156</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H8"/>
     </row>
@@ -2599,17 +2695,17 @@
         <v>0.75</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="9">
+        <v>55</v>
+      </c>
+      <c r="D9" s="6">
         <v>46156</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="6">
         <v>46156</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H9"/>
     </row>
@@ -2618,17 +2714,17 @@
         <v>0.5</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="9">
+        <v>60</v>
+      </c>
+      <c r="D10" s="6">
         <v>46157</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="6">
         <v>46158</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H10"/>
     </row>
@@ -2637,36 +2733,36 @@
         <v>0.25</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="9">
+        <v>61</v>
+      </c>
+      <c r="D11" s="6">
         <v>46157</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="6">
         <v>46158</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H11"/>
     </row>
     <row r="12" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="B12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="9">
+        <v>62</v>
+      </c>
+      <c r="D12" s="6">
         <v>46157</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="6">
         <v>46158</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H12"/>
     </row>
@@ -2675,17 +2771,17 @@
         <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="9">
+        <v>63</v>
+      </c>
+      <c r="D13" s="6">
         <v>46157</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="6">
         <v>46158</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H13"/>
     </row>
@@ -2694,17 +2790,17 @@
         <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="10">
+        <v>30</v>
+      </c>
+      <c r="D14" s="7">
         <v>46157</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="6">
         <v>46159</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H14"/>
     </row>
@@ -2713,17 +2809,17 @@
         <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="10">
-        <v>46158</v>
-      </c>
-      <c r="E15" s="9">
+        <v>42</v>
+      </c>
+      <c r="D15" s="7">
+        <v>46158</v>
+      </c>
+      <c r="E15" s="6">
         <v>46159</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H15"/>
     </row>
@@ -2732,17 +2828,17 @@
         <v>0</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="9">
-        <v>46158</v>
-      </c>
-      <c r="E16" s="9">
+        <v>43</v>
+      </c>
+      <c r="D16" s="6">
+        <v>46158</v>
+      </c>
+      <c r="E16" s="6">
         <v>46159</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H16"/>
     </row>
@@ -2811,43 +2907,43 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1"/>
-      <c r="B3" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11"/>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="13"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
-      <c r="F3" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="14"/>
+      <c r="F3" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" s="15"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1"/>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="11"/>
+      <c r="C4" s="13"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="7"/>
-      <c r="H4" s="8"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="12"/>
     </row>
     <row r="6" spans="1:8" ht="17.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
+      <c r="B6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1"/>
@@ -2870,7 +2966,7 @@
         <v>11</v>
       </c>
       <c r="H7" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="31.5">
@@ -2879,17 +2975,17 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="9">
+        <v>54</v>
+      </c>
+      <c r="D8" s="6">
         <v>46156</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="6">
         <v>46156</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="31.5">
@@ -2898,17 +2994,17 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9" s="9">
+        <v>65</v>
+      </c>
+      <c r="D9" s="6">
         <v>46156</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="6">
         <v>46156</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="31.5">
@@ -2917,17 +3013,17 @@
         <v>0.5</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="9">
+        <v>60</v>
+      </c>
+      <c r="D10" s="6">
         <v>46157</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="6">
         <v>46158</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2936,55 +3032,55 @@
         <v>0.25</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="9">
+        <v>61</v>
+      </c>
+      <c r="D11" s="6">
         <v>46157</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="6">
         <v>46158</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1"/>
       <c r="B12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="10">
-        <v>46158</v>
-      </c>
-      <c r="E12" s="9">
+        <v>57</v>
+      </c>
+      <c r="D12" s="7">
+        <v>46158</v>
+      </c>
+      <c r="E12" s="6">
         <v>46159</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1"/>
       <c r="B13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" s="10">
-        <v>46158</v>
-      </c>
-      <c r="E13" s="9">
+        <v>58</v>
+      </c>
+      <c r="D13" s="7">
+        <v>46158</v>
+      </c>
+      <c r="E13" s="6">
         <v>46159</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -2993,17 +3089,17 @@
         <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="10">
+        <v>30</v>
+      </c>
+      <c r="D14" s="7">
         <v>46157</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="6">
         <v>46159</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -3012,17 +3108,17 @@
         <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="10">
-        <v>46158</v>
-      </c>
-      <c r="E15" s="9">
+        <v>42</v>
+      </c>
+      <c r="D15" s="7">
+        <v>46158</v>
+      </c>
+      <c r="E15" s="6">
         <v>46159</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="31.5">
@@ -3031,17 +3127,17 @@
         <v>0</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="9">
-        <v>46158</v>
-      </c>
-      <c r="E16" s="9">
+        <v>43</v>
+      </c>
+      <c r="D16" s="6">
+        <v>46158</v>
+      </c>
+      <c r="E16" s="6">
         <v>46159</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -3109,43 +3205,43 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1"/>
-      <c r="B3" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11"/>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="13"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
-      <c r="F3" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="14"/>
+      <c r="F3" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="15"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1"/>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="11"/>
+      <c r="C4" s="13"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="7"/>
-      <c r="H4" s="8"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="12"/>
     </row>
     <row r="6" spans="1:8" ht="17.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
+      <c r="B6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1"/>
@@ -3168,7 +3264,7 @@
         <v>11</v>
       </c>
       <c r="H7" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -3177,17 +3273,17 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8" s="9">
+        <v>67</v>
+      </c>
+      <c r="D8" s="6">
         <v>46156</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="6">
         <v>46156</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="31.5">
@@ -3196,17 +3292,17 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" s="9">
+        <v>68</v>
+      </c>
+      <c r="D9" s="6">
         <v>46156</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="6">
         <v>46156</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -3215,17 +3311,17 @@
         <v>0.5</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D10" s="9">
+        <v>69</v>
+      </c>
+      <c r="D10" s="6">
         <v>46157</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="6">
         <v>46158</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -3234,17 +3330,17 @@
         <v>0.25</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="9">
+        <v>70</v>
+      </c>
+      <c r="D11" s="6">
         <v>46157</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="6">
         <v>46158</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="31.5">
@@ -3253,17 +3349,17 @@
         <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12" s="10">
-        <v>46158</v>
-      </c>
-      <c r="E12" s="9">
+        <v>71</v>
+      </c>
+      <c r="D12" s="7">
+        <v>46158</v>
+      </c>
+      <c r="E12" s="6">
         <v>46159</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -3272,74 +3368,74 @@
         <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="9">
+        <v>29</v>
+      </c>
+      <c r="D13" s="6">
         <v>46159</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="6">
         <v>46159</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1"/>
       <c r="B14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="10">
+        <v>30</v>
+      </c>
+      <c r="D14" s="7">
         <v>46157</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="6">
         <v>46159</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1"/>
       <c r="B15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="10">
-        <v>46158</v>
-      </c>
-      <c r="E15" s="9">
+        <v>42</v>
+      </c>
+      <c r="D15" s="7">
+        <v>46158</v>
+      </c>
+      <c r="E15" s="6">
         <v>46159</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1"/>
       <c r="B16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="9">
-        <v>46158</v>
-      </c>
-      <c r="E16" s="9">
+        <v>43</v>
+      </c>
+      <c r="D16" s="6">
+        <v>46158</v>
+      </c>
+      <c r="E16" s="6">
         <v>46159</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -3407,43 +3503,43 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1"/>
-      <c r="B3" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11"/>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="13"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
-      <c r="F3" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="14"/>
+      <c r="F3" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" s="15"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1"/>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="11"/>
+      <c r="C4" s="13"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="7"/>
-      <c r="H4" s="8"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="12"/>
     </row>
     <row r="6" spans="1:8" ht="17.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
+      <c r="B6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1"/>
@@ -3466,7 +3562,7 @@
         <v>11</v>
       </c>
       <c r="H7" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="31.5">
@@ -3475,169 +3571,169 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="9">
+        <v>54</v>
+      </c>
+      <c r="D8" s="6">
         <v>46156</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="6">
         <v>46156</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1"/>
       <c r="B9" s="3">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="9">
+        <v>55</v>
+      </c>
+      <c r="D9" s="6">
         <v>46156</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="6">
         <v>46156</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1"/>
       <c r="B10" s="3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D10" s="9">
+        <v>69</v>
+      </c>
+      <c r="D10" s="6">
         <v>46157</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="6">
         <v>46158</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="31.5">
       <c r="A11" s="1"/>
       <c r="B11" s="3">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="9">
+        <v>70</v>
+      </c>
+      <c r="D11" s="6">
         <v>46157</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="6">
         <v>46158</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="63.75">
       <c r="A12" s="1"/>
       <c r="B12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="9">
+        <v>62</v>
+      </c>
+      <c r="D12" s="6">
         <v>46157</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="6">
         <v>46158</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="31.5">
       <c r="A13" s="1"/>
       <c r="B13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="9">
+        <v>63</v>
+      </c>
+      <c r="D13" s="6">
         <v>46157</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="6">
         <v>46158</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1"/>
       <c r="B14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="10">
+        <v>30</v>
+      </c>
+      <c r="D14" s="7">
         <v>46157</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="6">
         <v>46159</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1"/>
       <c r="B15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="10">
-        <v>46158</v>
-      </c>
-      <c r="E15" s="9">
+        <v>42</v>
+      </c>
+      <c r="D15" s="7">
+        <v>46158</v>
+      </c>
+      <c r="E15" s="6">
         <v>46159</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="31.5">
       <c r="A16" s="1"/>
       <c r="B16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="9">
-        <v>46158</v>
-      </c>
-      <c r="E16" s="9">
+        <v>43</v>
+      </c>
+      <c r="D16" s="6">
+        <v>46158</v>
+      </c>
+      <c r="E16" s="6">
         <v>46159</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
